--- a/chicago/reference/resident-research/T-0463/T-0463_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0463/T-0463_resident_research_working.xlsx
@@ -1214,7 +1214,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839</t>
+          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839; isa_public_domain_land_tract_sales</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839</t>
+          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839; isa_public_domain_land_tract_sales</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_democrat_1833_11_26; fergus_chicago_directory_1839</t>
+          <t>andreas_1884_v1; chicago_democrat_1833_11_26; fergus_chicago_directory_1839; isa_public_domain_land_tract_sales</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_democrat_1833_11_26</t>
+          <t>andreas_1884_v1; chicago_democrat_1833_11_26; isa_public_domain_land_tract_sales</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0463/T-0463_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0463/T-0463_resident_research_working.xlsx
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; calumet_club_early_chicago_1879; chicago_democrat_1833_11_26</t>
+          <t>andreas_1884_v1; calumet_club_early_chicago_1879; chicago_american_1835; chicago_democrat_1833_11_26; fergus_chicago_directory_1839; fergus_chicago_directory_1843; norris_directory_1844</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_american_1835; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839; norris_directory_1844</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_democrat_1833_11_26; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; blackhawk_war_chicago_enrollments_isa; chicago_democrat_1833_11_26; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0463/T-0463_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0463/T-0463_resident_research_working.xlsx
@@ -2438,7 +2438,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_american_1835; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839; norris_directory_1844</t>
+          <t>andreas_1884_v1; chicago_american_1835; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839; isa_public_domain_land_tract_sales; norris_directory_1844</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0463/T-0463_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0463/T-0463_resident_research_working.xlsx
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; calumet_club_early_chicago_1879; chicago_democrat_1833_11_26</t>
+          <t>andreas_1884_v1; calumet_club_early_chicago_1879; chicago_american_1835; chicago_democrat_1833_11_26; fergus_chicago_directory_1839; fergus_chicago_directory_1843; norris_directory_1844</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_american_1835; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; norris_directory_1844</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_democrat_1833_11_26; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; blackhawk_war_chicago_enrollments_isa; chicago_democrat_1833_11_26; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_1843_old_settler_death_notices; fergus_chicago_directory_1839; fergus_chicago_directory_1843</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0463/T-0463_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0463/T-0463_resident_research_working.xlsx
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; calumet_club_early_chicago_1879; chicago_democrat_1833_11_26</t>
+          <t>andreas_1884_v1; calumet_club_early_chicago_1879; chicago_american_1835; chicago_democrat_1833_11_26; fergus_chicago_directory_1839; fergus_chicago_directory_1843; norris_directory_1844</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_american_1835; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839; isa_public_domain_land_tract_sales; norris_directory_1844</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_democrat_1833_11_26; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; blackhawk_war_chicago_enrollments_isa; chicago_democrat_1833_11_26; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0463/T-0463_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0463/T-0463_resident_research_working.xlsx
@@ -1727,7 +1727,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>uncertain (inferred)</t>
+          <t>present (inferred)</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">

--- a/chicago/reference/resident-research/T-0463/T-0463_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0463/T-0463_resident_research_working.xlsx
@@ -2713,7 +2713,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>saddler (attested)</t>
+          <t>none_recorded (reconstructed)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
